--- a/Planillas/Datos de estacas.xlsx
+++ b/Planillas/Datos de estacas.xlsx
@@ -9,16 +9,18 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="20490" windowHeight="7335"/>
+    <workbookView xWindow="0" yWindow="1200" windowWidth="20490" windowHeight="7335"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
-    <sheet name="entre estacas" sheetId="2" r:id="rId2"/>
-    <sheet name="a costa" sheetId="4" r:id="rId3"/>
+    <sheet name="Hoja1" sheetId="5" r:id="rId2"/>
+    <sheet name="entre estacas" sheetId="2" r:id="rId3"/>
+    <sheet name="a costa" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="estacas_costaUTM44" localSheetId="2">'a costa'!$A$1:$D$45</definedName>
-    <definedName name="matriz_de_distancia_estacas" localSheetId="1">'entre estacas'!$A$1:$C$1893</definedName>
+    <definedName name="estaca_senderoping" localSheetId="1">Hoja1!$A$1:$D$45</definedName>
+    <definedName name="estacas_costaUTM44" localSheetId="3">'a costa'!$A$1:$D$45</definedName>
+    <definedName name="matriz_de_distancia_estacas" localSheetId="2">'entre estacas'!$A$1:$C$1893</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
@@ -26,7 +28,39 @@
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <connection id="1" name="estacas_costaUTM44" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="1" name="estaca_senderoping" type="6" refreshedVersion="6" background="1" saveData="1">
+    <textPr sourceFile="E:\Análisis_R\Pinguinos\Qgis\estaca_senderoping.csv" decimal="," thousands="." tab="0" comma="1">
+      <textFields count="26">
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+      </textFields>
+    </textPr>
+  </connection>
+  <connection id="2" name="estacas_costaUTM44" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="437" sourceFile="E:\Análisis_R\Pinguinos\Qgis\estacas_costaUTM44.csv" decimal="," thousands="." tab="0" comma="1">
       <textFields count="25">
         <textField/>
@@ -57,7 +91,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="2" name="matriz de distancia estacas" type="6" refreshedVersion="6" background="1" saveData="1">
+  <connection id="3" name="matriz de distancia estacas" type="6" refreshedVersion="6" background="1" saveData="1">
     <textPr codePage="437" sourceFile="E:\Análisis_R\Pinguinos\Qgis\matriz de distancia estacas.csv" decimal="," thousands="." tab="0" comma="1">
       <textFields count="3">
         <textField/>
@@ -70,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3984" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4076" uniqueCount="73">
   <si>
     <t>estaca</t>
   </si>
@@ -284,14 +318,20 @@
   <si>
     <t>distancia a mar (m)</t>
   </si>
+  <si>
+    <t>distance</t>
+  </si>
+  <si>
+    <t>Sendero PingÃ¼inera</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="167" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="171" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -367,12 +407,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="171" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -394,11 +434,15 @@
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="matriz de distancia estacas" connectionId="2" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="estaca_senderoping" connectionId="1" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="estacas_costaUTM44" connectionId="1" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="matriz de distancia estacas" connectionId="3" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="estacas_costaUTM44" connectionId="2" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4991,6 +5035,652 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" s="7">
+        <v>297632102981092</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" s="7">
+        <v>272619445895269</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="7">
+        <v>220748873776426</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="7">
+        <v>228665635492404</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" s="7">
+        <v>32049634933885</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="7">
+        <v>34488285111943</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="7">
+        <v>322099212654428</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="7">
+        <v>427350516846915</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="7">
+        <v>444983404770935</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" s="7">
+        <v>557457446738615</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" s="7">
+        <v>534010683089633</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" s="7">
+        <v>223443090562166</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="7">
+        <v>665188008649852</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="7">
+        <v>637514910969664</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" s="7">
+        <v>768377296729782</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" s="7">
+        <v>749227149946306</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" s="7">
+        <v>881400380802898</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" s="7">
+        <v>836827481473982</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" s="7">
+        <v>951018418629513</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" s="7">
+        <v>982360452300457</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22" s="7">
+        <v>106458874714769</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" s="7">
+        <v>11256278821644</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" s="7">
+        <v>143114878920991</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" s="7">
+        <v>120199257766634</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" t="s">
+        <v>72</v>
+      </c>
+      <c r="D26" s="7">
+        <v>12664559063561</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" s="7">
+        <v>131332606304037</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" t="s">
+        <v>72</v>
+      </c>
+      <c r="D28" s="7">
+        <v>126536998890325</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" t="s">
+        <v>72</v>
+      </c>
+      <c r="D29" s="7">
+        <v>137305167613614</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" s="7">
+        <v>143672198388149</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" t="s">
+        <v>72</v>
+      </c>
+      <c r="D31" s="7">
+        <v>150378316567846</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" t="s">
+        <v>72</v>
+      </c>
+      <c r="D32" s="7">
+        <v>157344506506981</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" t="s">
+        <v>72</v>
+      </c>
+      <c r="D33" s="7">
+        <v>161491962334277</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>51</v>
+      </c>
+      <c r="C34" t="s">
+        <v>72</v>
+      </c>
+      <c r="D34" s="7">
+        <v>165798523445298</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" t="s">
+        <v>72</v>
+      </c>
+      <c r="D35" s="7">
+        <v>77337637242765</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>53</v>
+      </c>
+      <c r="C36" t="s">
+        <v>72</v>
+      </c>
+      <c r="D36" s="7">
+        <v>171773768440774</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" t="s">
+        <v>72</v>
+      </c>
+      <c r="D37" s="7">
+        <v>176505538082324</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C38" t="s">
+        <v>72</v>
+      </c>
+      <c r="D38" s="7">
+        <v>18482240142669</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>56</v>
+      </c>
+      <c r="C39" t="s">
+        <v>72</v>
+      </c>
+      <c r="D39" s="7">
+        <v>142533786879209</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>57</v>
+      </c>
+      <c r="C40" t="s">
+        <v>72</v>
+      </c>
+      <c r="D40" s="7">
+        <v>46327378022124</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41" t="s">
+        <v>72</v>
+      </c>
+      <c r="D41" s="7">
+        <v>416371105514468</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>59</v>
+      </c>
+      <c r="C42" t="s">
+        <v>72</v>
+      </c>
+      <c r="D42" s="7">
+        <v>195458638344472</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>60</v>
+      </c>
+      <c r="C43" t="s">
+        <v>72</v>
+      </c>
+      <c r="D43" s="7">
+        <v>49135145396704</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>61</v>
+      </c>
+      <c r="C44" t="s">
+        <v>72</v>
+      </c>
+      <c r="D44" s="7">
+        <v>159272674845931</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>62</v>
+      </c>
+      <c r="C45" t="s">
+        <v>72</v>
+      </c>
+      <c r="D45" s="7">
+        <v>125749877984689</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -25829,7 +26519,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
